--- a/data/trans_orig/IP2907_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP2907_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20467</t>
+          <t>20066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20869</t>
+          <t>20360</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45885</t>
+          <t>44899</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>32358</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60489</t>
+          <t>58907</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79673</t>
+          <t>80074</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91726</t>
+          <t>92153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86781</t>
+          <t>87767</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>111797</t>
+          <t>112306</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172317</t>
+          <t>173899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200310</t>
+          <t>200448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,1%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22256</t>
+          <t>21947</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12544</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26152</t>
+          <t>26437</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25151</t>
+          <t>25931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42425</t>
+          <t>43450</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71136</t>
+          <t>71445</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83561</t>
+          <t>83000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67092</t>
+          <t>66807</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80700</t>
+          <t>80872</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144212</t>
+          <t>143187</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>161486</t>
+          <t>160706</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,11%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13672</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13596</t>
+          <t>14218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10960</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34777</t>
+          <t>34619</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43412</t>
+          <t>43208</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48379</t>
+          <t>47757</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57539</t>
+          <t>57683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86290</t>
+          <t>85742</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99464</t>
+          <t>98843</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31894</t>
+          <t>32015</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50853</t>
+          <t>50961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30950</t>
+          <t>31608</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56084</t>
+          <t>55071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69639</t>
+          <t>68985</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101521</t>
+          <t>100384</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>133982</t>
+          <t>133874</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152941</t>
+          <t>152820</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154822</t>
+          <t>155835</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179956</t>
+          <t>179298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>294220</t>
+          <t>295357</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>326102</t>
+          <t>326756</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,57%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29625</t>
+          <t>30496</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20067</t>
+          <t>19711</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40484</t>
+          <t>40476</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40206</t>
+          <t>39033</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64040</t>
+          <t>64235</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85175</t>
+          <t>84304</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99383</t>
+          <t>98683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117571</t>
+          <t>117579</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137988</t>
+          <t>138344</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>208815</t>
+          <t>208620</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>232649</t>
+          <t>233822</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,69%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>21786</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22527</t>
+          <t>22703</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22774</t>
+          <t>22004</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39492</t>
+          <t>39698</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>45604</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56762</t>
+          <t>57452</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45541</t>
+          <t>45365</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58670</t>
+          <t>58814</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95966</t>
+          <t>95760</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112684</t>
+          <t>113454</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,76%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99128</t>
+          <t>98657</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132162</t>
+          <t>130526</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121508</t>
+          <t>122005</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169765</t>
+          <t>167452</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>233330</t>
+          <t>235315</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>290111</t>
+          <t>289077</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>476844</t>
+          <t>478480</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>509878</t>
+          <t>510349</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>555150</t>
+          <t>557463</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>603407</t>
+          <t>602910</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1043810</t>
+          <t>1044844</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1100591</t>
+          <t>1098606</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2907_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP2907_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23372</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16429</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32236</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19,68%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,83%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>13100</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7987</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20066</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>29860</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20360</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44899</t>
+          <t>20073</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>42960</t>
+          <t>36473</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32358</t>
+          <t>27524</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58907</t>
+          <t>45944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87040</t>
+          <t>95418</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80074</t>
+          <t>86554</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92153</t>
+          <t>102361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>102806</t>
+          <t>85665</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87767</t>
+          <t>78692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112306</t>
+          <t>90428</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>189846</t>
+          <t>181081</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173899</t>
+          <t>171610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200448</t>
+          <t>190030</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118790</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118790</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118790</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>100140</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>100140</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>100140</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>132666</t>
+          <t>98765</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>132666</t>
+          <t>98765</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>132666</t>
+          <t>98765</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>232806</t>
+          <t>217554</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>232806</t>
+          <t>217554</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>232806</t>
+          <t>217554</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17289</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11422</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24162</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15178</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10392</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21947</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>16,25%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26437</t>
+          <t>21885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>33574</t>
+          <t>32626</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25931</t>
+          <t>23878</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43450</t>
+          <t>41553</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72184</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>65311</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>78051</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>80,68%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>72,99%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,23%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>78214</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>71445</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>83000</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>83,75%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,87%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>74848</t>
+          <t>80073</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66807</t>
+          <t>73525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80872</t>
+          <t>85540</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>153063</t>
+          <t>152257</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143187</t>
+          <t>143330</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>160706</t>
+          <t>161005</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89473</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89473</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89473</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93244</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93244</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93244</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>186637</t>
+          <t>184883</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>186637</t>
+          <t>184883</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>186637</t>
+          <t>184883</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8143</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4551</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13715</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14,66%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8838</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5241</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13830</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,24%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>28,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8408</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4897</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14218</t>
+          <t>14128</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17246</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>11508</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>24819</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>47398</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>41826</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>50990</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>85,34%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,81%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>39611</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>34619</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>43208</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>81,76%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>71,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,18%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53567</t>
+          <t>40889</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47757</t>
+          <t>35603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57683</t>
+          <t>44834</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>93178</t>
+          <t>88288</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85742</t>
+          <t>80453</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98843</t>
+          <t>93764</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55541</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55541</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55541</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>48449</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>48449</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>48449</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>61975</t>
+          <t>49731</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61975</t>
+          <t>49731</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61975</t>
+          <t>49731</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>110424</t>
+          <t>105272</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>110424</t>
+          <t>105272</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110424</t>
+          <t>105272</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38438</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28656</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>52875</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>40466</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>32015</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>50961</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>21,89%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,32%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42334</t>
+          <t>39153</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31608</t>
+          <t>30556</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55071</t>
+          <t>48278</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>82800</t>
+          <t>77591</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68985</t>
+          <t>63220</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100384</t>
+          <t>93197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>157171</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>142734</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>166953</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>72,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>144369</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>133874</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>152820</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>78,11%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>72,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>82,68%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>168572</t>
+          <t>130662</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155835</t>
+          <t>121537</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179298</t>
+          <t>139259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>312941</t>
+          <t>287833</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>295357</t>
+          <t>272227</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>326756</t>
+          <t>302204</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,7%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>195609</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>195609</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>195609</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>184835</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>184835</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>184835</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>210906</t>
+          <t>169815</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>210906</t>
+          <t>169815</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>210906</t>
+          <t>169815</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>395741</t>
+          <t>365424</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>395741</t>
+          <t>365424</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>395741</t>
+          <t>365424</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26798</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18396</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35917</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,59%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24,92%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>22047</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>16117</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>30496</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>19,2%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29361</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19711</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40476</t>
+          <t>29729</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>51408</t>
+          <t>48567</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39033</t>
+          <t>37909</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64235</t>
+          <t>62068</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>117332</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>108213</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>125734</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,41%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>75,08%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>92753</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>84304</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>98683</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>80,8%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>73,44%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>85,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>128694</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117579</t>
+          <t>84911</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138344</t>
+          <t>99303</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>221447</t>
+          <t>210203</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>208620</t>
+          <t>196702</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233822</t>
+          <t>220861</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>144130</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>144130</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>144130</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>114800</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>114800</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>114800</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>158055</t>
+          <t>114640</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>158055</t>
+          <t>114640</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158055</t>
+          <t>114640</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>272855</t>
+          <t>258770</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>272855</t>
+          <t>258770</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>272855</t>
+          <t>258770</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14357</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9222</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>22064</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>22,12%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>14,21%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>33,99%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>15425</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>9938</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>21786</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>22,89%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>14,75%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>32,33%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>15771</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>11052</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22703</t>
+          <t>22874</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>30481</t>
+          <t>30127</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22004</t>
+          <t>22913</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39698</t>
+          <t>39356</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>50553</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>42846</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>55688</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>77,88%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>66,01%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>85,79%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>51965</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>45604</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>57452</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>77,11%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>67,67%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>85,25%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>53012</t>
+          <t>52992</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45365</t>
+          <t>45889</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58814</t>
+          <t>57711</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>104977</t>
+          <t>103546</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95760</t>
+          <t>94317</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>113454</t>
+          <t>110760</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>82,86%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>64910</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>64910</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>64910</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>67390</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>67390</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>67390</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>68068</t>
+          <t>68763</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68068</t>
+          <t>68763</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68068</t>
+          <t>68763</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>135458</t>
+          <t>133673</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>135458</t>
+          <t>133673</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>135458</t>
+          <t>133673</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>128397</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>109737</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>149043</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>19,21%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>22,3%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>115054</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>98657</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>130526</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>18,89%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>16,2%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>21,43%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>143414</t>
+          <t>113972</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>122005</t>
+          <t>98092</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>167452</t>
+          <t>130207</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>258467</t>
+          <t>242368</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>235315</t>
+          <t>217680</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>289077</t>
+          <t>269679</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>540055</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>519409</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>558715</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>80,79%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>77,7%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>83,58%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>718</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>493952</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>478480</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>510349</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>81,11%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>78,57%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>83,8%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>581501</t>
+          <t>483152</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>557463</t>
+          <t>466917</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>602910</t>
+          <t>499032</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1075454</t>
+          <t>1023208</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1044844</t>
+          <t>995897</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1098606</t>
+          <t>1047896</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>668452</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>668452</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>668452</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>891</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>609006</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>609006</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>609006</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>912</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>724915</t>
+          <t>597124</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>724915</t>
+          <t>597124</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>724915</t>
+          <t>597124</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1333921</t>
+          <t>1265576</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1333921</t>
+          <t>1265576</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1333921</t>
+          <t>1265576</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
